--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Petr Vershinin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Petr Vershinin\Desktop\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
   <si>
     <t>Код</t>
   </si>
@@ -199,6 +199,42 @@
   </si>
   <si>
     <t>+E</t>
+  </si>
+  <si>
+    <t>Обработка заявок менеджером по депозитным процессам в бек-офисе</t>
+  </si>
+  <si>
+    <t>Возможность подачи заявки сотрудником отделения напрямую в АБС</t>
+  </si>
+  <si>
+    <t>Обработка заявок сотрудником колл-центра</t>
+  </si>
+  <si>
+    <t>Менеджер должен подтверждать условия депозита в АБС банка.</t>
+  </si>
+  <si>
+    <t>Сценарий для клиентов, которые приходят в отделение для открытия депозита.</t>
+  </si>
+  <si>
+    <t>Заявки с сайта должны поступать в систему колл-центра для отправки в АБС.</t>
+  </si>
+  <si>
+    <t>Возможность переключения на резервный ЦОД</t>
+  </si>
+  <si>
+    <t>Обеспечение бесшовного переключения при сбоях в основном ЦОД.</t>
+  </si>
+  <si>
+    <t>Избегание прямого обмена данными между онлайн-банком и АБС</t>
+  </si>
+  <si>
+    <t>Для снижения нагрузки на АБС и предотвращения ошибок.</t>
+  </si>
+  <si>
+    <t>Не нагружать базу АБС ненужными данными</t>
+  </si>
+  <si>
+    <t>Следует минимизировать объем данных, которые отправляются в АБС и не требуются ей в данный момент.</t>
   </si>
 </sst>
 </file>
@@ -280,7 +316,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -371,19 +407,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -404,9 +460,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -426,6 +479,37 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -654,288 +738,344 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.85546875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="56.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="69.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="56.85546875" style="24" customWidth="1"/>
+    <col min="4" max="4" width="69.7109375" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="16"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="16"/>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="16"/>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="16"/>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="17"/>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="16"/>
+      <c r="C9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="19"/>
+      <c r="C10" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="19"/>
+      <c r="C11" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="20"/>
+      <c r="C12" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="16"/>
-      <c r="C11" s="11" t="s">
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="13"/>
+      <c r="C14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D14" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="17"/>
-      <c r="C12" s="11" t="s">
+    <row r="15" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="14"/>
+      <c r="C15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="15" t="s">
+    <row r="16" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="16"/>
-      <c r="C14" s="11" t="s">
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="13"/>
+      <c r="C17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D17" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="17"/>
-      <c r="C15" s="11" t="s">
+    <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="16"/>
+      <c r="C18" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D18" s="17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="15" t="s">
+    <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="20"/>
+      <c r="C19" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="10"/>
-    </row>
-    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="16"/>
-      <c r="C17" s="11" t="s">
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="13"/>
+      <c r="C21" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D21" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="17"/>
-      <c r="C18" s="11" t="s">
+    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="14"/>
+      <c r="C22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D22" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="15" t="s">
+    <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="16"/>
-      <c r="C20" s="11" t="s">
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="13"/>
+      <c r="C24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D24" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="17"/>
-      <c r="C21" s="11" t="s">
+    <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="14"/>
+      <c r="C25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D25" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="15" t="s">
+    <row r="26" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="10"/>
-    </row>
-    <row r="23" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="11" t="s">
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D27" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="11" t="s">
+    <row r="28" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="11" t="s">
+    <row r="29" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D29" s="17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="18" t="s">
+    <row r="30" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="21"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="21"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C32" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="10"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="17"/>
-      <c r="C27" s="2" t="s">
+      <c r="D32" s="8"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B33" s="14"/>
+      <c r="C33" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D33" s="26" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="17"/>
-      <c r="C28" s="2" t="s">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B34" s="14"/>
+      <c r="C34" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D34" s="26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="18" t="s">
+    <row r="35" spans="2:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C35" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="10"/>
-    </row>
-    <row r="30" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B30" s="17"/>
-      <c r="C30" s="2" t="s">
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="2:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B36" s="14"/>
+      <c r="C36" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D36" s="26" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="18" t="s">
+    <row r="37" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C37" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="10"/>
-    </row>
-    <row r="32" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B32" s="17"/>
-      <c r="C32" s="2" t="s">
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="2:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B38" s="14"/>
+      <c r="C38" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D38" s="26" t="s">
         <v>57</v>
       </c>
     </row>
